--- a/testAutomation_v1.0/test/Manual/Builder/NEMO-24402/NEMO-24402_builder_clone_ebook_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/Builder/NEMO-24402/NEMO-24402_builder_clone_ebook_test_cases.xlsx
@@ -372,7 +372,7 @@
     <t>Logged in as Admin (harishthoradmin) on Builder Thor. eBook "cqacloneebook15june26" (non-ingested) visible in listing. Code my_ebook_01 does not already exist.</t>
   </si>
   <si>
-    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / C0&gt;pr0!899
+    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / {{env.BLDR_THOR_VALIDADMIN_PASSWORD}}
 2. Navigate to eBooks listing page [ASSUMED: left nav or top menu]
 3. Locate cqacloneebook15june26
 4. Click Clone action for cqacloneebook15june26 [ASSUMED: context menu / action button]
@@ -398,7 +398,7 @@
     <t>Logged in as Admin (harishthoradmin) on Builder Thor. eBook "cqacloneebook15june26" (non-ingested) visible in listing. Code ebook_2024 does not exist.</t>
   </si>
   <si>
-    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / C0&gt;pr0!899
+    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / {{env.BLDR_THOR_VALIDADMIN_PASSWORD}}
 2. Navigate to eBooks listing page [ASSUMED: left nav or top menu]
 3. Locate cqacloneebook15june26
 4. Click Clone action for cqacloneebook15june26 [ASSUMED: context menu / action button]
@@ -421,7 +421,7 @@
     <t>Logged in as Admin (harishthoradmin) on Builder Thor. eBook "cqacloneebook15june26" (non-ingested) visible in listing. Code ebook_a_2_b does not exist.</t>
   </si>
   <si>
-    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / C0&gt;pr0!899
+    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / {{env.BLDR_THOR_VALIDADMIN_PASSWORD}}
 2. Navigate to eBooks listing page [ASSUMED: left nav or top menu]
 3. Locate cqacloneebook15june26
 4. Click Clone action for cqacloneebook15june26 [ASSUMED: context menu / action button]
@@ -447,7 +447,7 @@
     <t>Logged in as Admin (harishthoradmin) on Builder Thor. eBook "cqacloneebook15june26" (non-ingested) visible in listing. Code unique_ebook_01 does not exist.</t>
   </si>
   <si>
-    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / C0&gt;pr0!899
+    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / {{env.BLDR_THOR_VALIDADMIN_PASSWORD}}
 2. Navigate to eBooks listing page [ASSUMED: left nav or top menu]
 3. Click Clone action for cqacloneebook15june26 [ASSUMED: context menu / action button]
 4. Enter duplicate: cqacloneebook15june26
@@ -471,7 +471,7 @@
     <t>Logged in as Admin (harishthoradmin) on Builder Thor. eBook "cqacloneebook15june26" (non-ingested) visible in listing. Code regression_ebook_145 does not exist.</t>
   </si>
   <si>
-    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / C0&gt;pr0!899
+    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / {{env.BLDR_THOR_VALIDADMIN_PASSWORD}}
 2. Navigate to eBooks listing page [ASSUMED: left nav or top menu]
 3. Click Clone action for cqacloneebook15june26 [ASSUMED: context menu / action button]
 4. Enter unique code: regression_ebook_145
@@ -496,7 +496,7 @@
     <t>Logged in as Admin (harishthoradmin) on Builder Thor. eBook "cqacloneebook15june26" (non-ingested) visible in listing. Code reuse_ebook_del_01 does not exist.</t>
   </si>
   <si>
-    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / C0&gt;pr0!899
+    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / {{env.BLDR_THOR_VALIDADMIN_PASSWORD}}
 2. Navigate to eBooks listing page [ASSUMED: left nav or top menu]
 3. Click Clone action for cqacloneebook15june26 [ASSUMED: context menu / action button]
 4. Enter: reuse_ebook_del_01
@@ -521,7 +521,7 @@
     <t>Logged in as Admin (harishthoradmin) on Builder Thor. eBook "cqacloneebook15june26" (non-ingested) visible in listing. Code reuse_after_del_ebook does not exist.</t>
   </si>
   <si>
-    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / C0&gt;pr0!899
+    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / {{env.BLDR_THOR_VALIDADMIN_PASSWORD}}
 2. Navigate to eBooks listing page [ASSUMED: left nav or top menu]
 3. Clone cqacloneebook15june26 with code: reuse_after_del_ebook
 4. Confirm clone success
@@ -546,7 +546,7 @@
     <t>Logged in as Admin. Non-ingested Component cqaclone1_15junepe1 and eBook cqacloneebook15june26 exist. Code reuse_comp_on_ebook_01 does not exist.</t>
   </si>
   <si>
-    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / C0&gt;pr0!899
+    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / {{env.BLDR_THOR_VALIDADMIN_PASSWORD}}
 2. Navigate to Components listing
 3. Clone cqaclone1_15junepe1 with code: reuse_comp_on_ebook_01
 4. Confirm component clone success
@@ -572,7 +572,7 @@
     <t>Logged in as Admin (harishthoradmin) on Builder Thor. eBook "cqacloneebook15june26" (non-ingested) visible in listing.</t>
   </si>
   <si>
-    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / C0&gt;pr0!899
+    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / {{env.BLDR_THOR_VALIDADMIN_PASSWORD}}
 2. Navigate to eBooks listing page [ASSUMED: left nav or top menu]
 3. Click Clone action for cqacloneebook15june26 [ASSUMED: context menu / action button]
 4. Enter whitespace only (3+ spaces) in Unique Code field
@@ -591,7 +591,7 @@
     <t>Verify the duplicate code error is displayed inline near the code field, not as a browser alert dialog</t>
   </si>
   <si>
-    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / C0&gt;pr0!899
+    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / {{env.BLDR_THOR_VALIDADMIN_PASSWORD}}
 2. Navigate to eBooks listing page [ASSUMED: left nav or top menu]
 3. Click Clone action for cqacloneebook15june26 [ASSUMED: context menu / action button]
 4. Enter: cqacloneebook15june26 (own code)
@@ -611,7 +611,7 @@
     <t>Verify an inline uniqueness error is shown when cloning using the source eBook's own existing code</t>
   </si>
   <si>
-    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / C0&gt;pr0!899
+    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / {{env.BLDR_THOR_VALIDADMIN_PASSWORD}}
 2. Navigate to eBooks listing page [ASSUMED: left nav or top menu]
 3. Click Clone action for cqacloneebook15june26 [ASSUMED: context menu / action button]
 4. Enter code: cqacloneebook15june26
@@ -630,7 +630,7 @@
     <t>Logged in as Admin (harishthoradmin) on Builder Thor. eBook "cqacloneebook15june26" (non-ingested) visible in listing. Non-ingested component cqaclone1_15junepe1 exists.</t>
   </si>
   <si>
-    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / C0&gt;pr0!899
+    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / {{env.BLDR_THOR_VALIDADMIN_PASSWORD}}
 2. Navigate to eBooks listing page [ASSUMED: left nav or top menu]
 3. Click Clone action for cqacloneebook15june26 [ASSUMED: context menu / action button]
 4. Enter code: cqaclone1_15junepe1
@@ -652,7 +652,7 @@
     <t>Logged in as Admin (harishthoradmin) on Builder Thor. eBook "cqacloneebook15june26" (non-ingested) visible in listing. Umbrella cqaumbrellaforautotest15june2026 exists.</t>
   </si>
   <si>
-    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / C0&gt;pr0!899
+    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / {{env.BLDR_THOR_VALIDADMIN_PASSWORD}}
 2. Navigate to eBooks listing page [ASSUMED: left nav or top menu]
 3. Click Clone action for cqacloneebook15june26 [ASSUMED: context menu / action button]
 4. Enter code: cqaumbrellaforautotest15june2026
@@ -668,7 +668,7 @@
     <t>Verify a required-field error is shown when the unique code field is left empty</t>
   </si>
   <si>
-    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / C0&gt;pr0!899
+    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / {{env.BLDR_THOR_VALIDADMIN_PASSWORD}}
 2. Navigate to eBooks listing page [ASSUMED: left nav or top menu]
 3. Click Clone action for cqacloneebook15june26 [ASSUMED: context menu / action button]
 4. Leave Unique Code field empty
@@ -684,7 +684,7 @@
     <t>Verify a format error is shown when the unique code contains uppercase letters</t>
   </si>
   <si>
-    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / C0&gt;pr0!899
+    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / {{env.BLDR_THOR_VALIDADMIN_PASSWORD}}
 2. Navigate to eBooks listing page [ASSUMED: left nav or top menu]
 3. Click Clone action for cqacloneebook15june26 [ASSUMED: context menu / action button]
 4. Enter code: MyEbook_Invalid
@@ -700,7 +700,7 @@
     <t>Verify a format error is shown when the unique code contains special characters</t>
   </si>
   <si>
-    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / C0&gt;pr0!899
+    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / {{env.BLDR_THOR_VALIDADMIN_PASSWORD}}
 2. Navigate to eBooks listing page [ASSUMED: left nav or top menu]
 3. Click Clone action for cqacloneebook15june26 [ASSUMED: context menu / action button]
 4. Enter code: ebook-one@test
@@ -719,7 +719,7 @@
     <t>Logged in as Admin on Builder Thor. Ingested eBook cqa_test_ebook_11june visible in listing.</t>
   </si>
   <si>
-    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / C0&gt;pr0!899
+    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / {{env.BLDR_THOR_VALIDADMIN_PASSWORD}}
 2. Navigate to eBooks listing page [ASSUMED: left nav or top menu]
 3. Locate ingested eBook cqa_test_ebook_11june
 4. Open action menu [ASSUMED]
@@ -741,7 +741,7 @@
     <t>Logged in as Admin (harishthoradmin) on Builder Thor. eBook "cqacloneebook15june26" (non-ingested) visible in listing. Ingested eBook cqa_test_ebook_11june exists.</t>
   </si>
   <si>
-    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / C0&gt;pr0!899
+    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / {{env.BLDR_THOR_VALIDADMIN_PASSWORD}}
 2. Navigate to eBooks listing page [ASSUMED: left nav or top menu]
 3. Click Clone action for cqacloneebook15june26 [ASSUMED: context menu / action button]
 4. Enter code: cqa_test_ebook_11june
@@ -790,7 +790,7 @@
     <t>Logged in as Admin on Builder Thor. eBook cqacloneebook15june26 (non-ingested) visible. Code family_ebook_01 does not already exist anywhere.</t>
   </si>
   <si>
-    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / C0&gt;pr0!899
+    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / {{env.BLDR_THOR_VALIDADMIN_PASSWORD}}
 2. Left pane: click Families [ASSUMED]
 3. Click Create a Family [ASSUMED]
 4. Enter unique code: family_ebook_01 (lowercase letters + numbers)
@@ -816,7 +816,7 @@
     <t>Logged in as Admin on Builder Thor. eBook cqacloneebook15june26 visible. Family with code family_ebook_01 exists (created in TST_NEMO24402_TC_19 or fresh).</t>
   </si>
   <si>
-    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / C0&gt;pr0!899
+    <t>1. Login: https://asgard-thor-builder.comprodls.com/2024/pre-login | Org: Cambridge One | Confirm | IdP: harishthoradmin / {{env.BLDR_THOR_VALIDADMIN_PASSWORD}}
 2. Left pane: click Families [ASSUMED]
 3. Locate Family family_ebook_01
 4. Click Delete action for Family family_ebook_01 [ASSUMED]
